--- a/scenario_variables/other_experiment_data/dev0/sub0/run0price_scenarios188.xlsx
+++ b/scenario_variables/other_experiment_data/dev0/sub0/run0price_scenarios188.xlsx
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>30.0853187380475</v>
+        <v>24.3222498152266</v>
       </c>
     </row>
     <row r="3">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23.12369601522129</v>
+        <v>27.89373300919414</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>27.26532160975045</v>
+        <v>22.53624537957375</v>
       </c>
     </row>
     <row r="5">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>26.85861460724102</v>
+        <v>29.20023887505769</v>
       </c>
     </row>
     <row r="6">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>27.5733656442835</v>
+        <v>29.00367210488407</v>
       </c>
     </row>
     <row r="7">
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>28.26613509053244</v>
+        <v>21.10717422726262</v>
       </c>
     </row>
     <row r="8">
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>29.89369070365238</v>
+        <v>24.01071814964899</v>
       </c>
     </row>
     <row r="9">
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>22.87845444676072</v>
+        <v>27.66998386131983</v>
       </c>
     </row>
     <row r="10">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>27.21995466117444</v>
+        <v>22.24363754449088</v>
       </c>
     </row>
     <row r="11">
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>27.03054725563269</v>
+        <v>29.6485966989531</v>
       </c>
     </row>
     <row r="12">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>28.49678574744939</v>
+        <v>28.3498372540765</v>
       </c>
     </row>
     <row r="13">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>28.43509237705367</v>
+        <v>21.23561253000399</v>
       </c>
     </row>
     <row r="14">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>30.07374912477554</v>
+        <v>24.78734990183331</v>
       </c>
     </row>
     <row r="15">
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>23.04631774045898</v>
+        <v>27.81005233331799</v>
       </c>
     </row>
     <row r="16">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>26.74079508798118</v>
+        <v>22.92802461365091</v>
       </c>
     </row>
     <row r="17">
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>26.91463161036991</v>
+        <v>29.34683492468389</v>
       </c>
     </row>
     <row r="18">
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>27.98607992743867</v>
+        <v>28.22241443691294</v>
       </c>
     </row>
     <row r="19">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>29.08474204068694</v>
+        <v>21.80420308759002</v>
       </c>
     </row>
     <row r="20">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>29.93879149633678</v>
+        <v>24.25451863634803</v>
       </c>
     </row>
     <row r="21">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>23.133034898786</v>
+        <v>27.62423499186584</v>
       </c>
     </row>
     <row r="22">
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>27.25446368892001</v>
+        <v>22.72088485694135</v>
       </c>
     </row>
     <row r="23">
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>26.60714080600722</v>
+        <v>29.03824490175862</v>
       </c>
     </row>
     <row r="24">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>28.28887278626872</v>
+        <v>28.64239815147977</v>
       </c>
     </row>
     <row r="25">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>28.59897775964668</v>
+        <v>21.5928455283322</v>
       </c>
     </row>
     <row r="26">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>30.23377488268549</v>
+        <v>24.41124178783663</v>
       </c>
     </row>
     <row r="27">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>22.85375110243023</v>
+        <v>27.10304382534049</v>
       </c>
     </row>
     <row r="28">
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>27.64638430427586</v>
+        <v>22.5748069064596</v>
       </c>
     </row>
     <row r="29">
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>26.54436650136627</v>
+        <v>29.4690841415418</v>
       </c>
     </row>
     <row r="30">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>28.13337343288733</v>
+        <v>28.2698578943082</v>
       </c>
     </row>
     <row r="31">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>29.00731013014455</v>
+        <v>21.36351937224992</v>
       </c>
     </row>
     <row r="32">
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>29.69936687992453</v>
+        <v>24.21386822011661</v>
       </c>
     </row>
     <row r="33">
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>22.93287955853662</v>
+        <v>27.91110549862909</v>
       </c>
     </row>
     <row r="34">
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>27.29109635655066</v>
+        <v>22.65899836667525</v>
       </c>
     </row>
     <row r="35">
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>26.78622505916637</v>
+        <v>29.20183045221572</v>
       </c>
     </row>
     <row r="36">
@@ -1007,7 +1007,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>27.53552531550904</v>
+        <v>28.24840807754949</v>
       </c>
     </row>
     <row r="37">
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>28.40499949542222</v>
+        <v>21.51090972858892</v>
       </c>
     </row>
     <row r="38">
@@ -1039,7 +1039,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>29.6778391801997</v>
+        <v>24.15570058734892</v>
       </c>
     </row>
     <row r="39">
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>23.1727144963326</v>
+        <v>27.41305016574488</v>
       </c>
     </row>
     <row r="40">
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>27.01325632417877</v>
+        <v>22.36456620811508</v>
       </c>
     </row>
     <row r="41">
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>27.33903938453419</v>
+        <v>29.28005630107156</v>
       </c>
     </row>
     <row r="42">
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>27.75016405294309</v>
+        <v>28.6317260657358</v>
       </c>
     </row>
     <row r="43">
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>28.29411863393847</v>
+        <v>21.35096784984749</v>
       </c>
     </row>
     <row r="44">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>30.24051967523399</v>
+        <v>24.41600387169951</v>
       </c>
     </row>
     <row r="45">
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>22.77960732642177</v>
+        <v>27.10478106288278</v>
       </c>
     </row>
     <row r="46">
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>27.32594199225768</v>
+        <v>22.17203291826857</v>
       </c>
     </row>
     <row r="47">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>27.27367557567923</v>
+        <v>29.21111671926923</v>
       </c>
     </row>
     <row r="48">
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>27.51963325171168</v>
+        <v>28.51503250557316</v>
       </c>
     </row>
     <row r="49">
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>28.43794683967966</v>
+        <v>21.53140285197389</v>
       </c>
     </row>
     <row r="50">
@@ -1231,7 +1231,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>32.07303485763677</v>
+        <v>29.60743581495237</v>
       </c>
     </row>
     <row r="51">
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>30.84688142834338</v>
+        <v>29.47511091247202</v>
       </c>
     </row>
     <row r="52">
@@ -1263,7 +1263,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>22.44592923236874</v>
+        <v>26.01971537111919</v>
       </c>
     </row>
     <row r="53">
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>26.77590993869613</v>
+        <v>29.1691461233593</v>
       </c>
     </row>
     <row r="54">
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>31.15555976851631</v>
+        <v>27.72730277011543</v>
       </c>
     </row>
     <row r="55">
@@ -1311,7 +1311,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>29.89314116689913</v>
+        <v>24.47182744917067</v>
       </c>
     </row>
     <row r="56">
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>32.07003102410232</v>
+        <v>28.89853724508836</v>
       </c>
     </row>
     <row r="57">
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>30.71362376141913</v>
+        <v>29.69961381974606</v>
       </c>
     </row>
     <row r="58">
@@ -1359,7 +1359,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>22.57250208966166</v>
+        <v>26.06384889169911</v>
       </c>
     </row>
     <row r="59">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>27.1972255427317</v>
+        <v>28.60851923871857</v>
       </c>
     </row>
     <row r="60">
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>31.08462456199494</v>
+        <v>28.06937147997213</v>
       </c>
     </row>
     <row r="61">
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>29.59171622733891</v>
+        <v>24.4221912627969</v>
       </c>
     </row>
     <row r="62">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>32.58675798974242</v>
+        <v>29.24407517301526</v>
       </c>
     </row>
     <row r="63">
@@ -1439,7 +1439,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>30.75261314439343</v>
+        <v>28.8839964808188</v>
       </c>
     </row>
     <row r="64">
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>22.45630349820185</v>
+        <v>25.95809858699379</v>
       </c>
     </row>
     <row r="65">
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>27.31235595200049</v>
+        <v>28.72062370986848</v>
       </c>
     </row>
     <row r="66">
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>30.69169950130432</v>
+        <v>27.95710137335474</v>
       </c>
     </row>
     <row r="67">
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>30.03921361819298</v>
+        <v>25.05969087906914</v>
       </c>
     </row>
     <row r="68">
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>32.36053216632335</v>
+        <v>29.19282762480124</v>
       </c>
     </row>
     <row r="69">
@@ -1535,7 +1535,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>30.35639330082552</v>
+        <v>29.22489361270874</v>
       </c>
     </row>
     <row r="70">
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>22.9459986499997</v>
+        <v>25.93762494228854</v>
       </c>
     </row>
     <row r="71">
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>27.24621017196735</v>
+        <v>29.09049403707572</v>
       </c>
     </row>
     <row r="72">
@@ -1583,7 +1583,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>31.24857789629164</v>
+        <v>27.81600287553888</v>
       </c>
     </row>
     <row r="73">
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>30.36995805017136</v>
+        <v>24.20552269817229</v>
       </c>
     </row>
     <row r="74">
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>31.91139920571509</v>
+        <v>29.26182921912051</v>
       </c>
     </row>
     <row r="75">
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>30.37688390136735</v>
+        <v>29.291874354235</v>
       </c>
     </row>
     <row r="76">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>22.52489125549262</v>
+        <v>26.5012293273528</v>
       </c>
     </row>
     <row r="77">
@@ -1663,7 +1663,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>26.9128417096471</v>
+        <v>28.93886442892078</v>
       </c>
     </row>
     <row r="78">
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>30.96989355208163</v>
+        <v>28.33777770489776</v>
       </c>
     </row>
     <row r="79">
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>29.90630506594851</v>
+        <v>24.42525279592137</v>
       </c>
     </row>
     <row r="80">
@@ -1711,7 +1711,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>32.07841172142162</v>
+        <v>28.61918638447023</v>
       </c>
     </row>
     <row r="81">
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>30.86076514406685</v>
+        <v>29.39835026494288</v>
       </c>
     </row>
     <row r="82">
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>22.73000660611551</v>
+        <v>26.04844647201659</v>
       </c>
     </row>
     <row r="83">
@@ -1759,7 +1759,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>27.52861026891005</v>
+        <v>28.6480074318652</v>
       </c>
     </row>
     <row r="84">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>30.91176311031762</v>
+        <v>27.96904259784303</v>
       </c>
     </row>
     <row r="85">
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>30.61536224233168</v>
+        <v>24.58960675798619</v>
       </c>
     </row>
     <row r="86">
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>32.19004896545693</v>
+        <v>28.81590261733428</v>
       </c>
     </row>
     <row r="87">
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>30.34522911157405</v>
+        <v>28.79785268246499</v>
       </c>
     </row>
     <row r="88">
@@ -1839,7 +1839,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>22.48366936818038</v>
+        <v>26.09040672592899</v>
       </c>
     </row>
     <row r="89">
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>27.2651204035143</v>
+        <v>28.20553795586352</v>
       </c>
     </row>
     <row r="90">
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>30.92453070714119</v>
+        <v>28.27270521057375</v>
       </c>
     </row>
     <row r="91">
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>30.01743117264935</v>
+        <v>24.19143862040937</v>
       </c>
     </row>
     <row r="92">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>32.14128685154849</v>
+        <v>28.59890296490356</v>
       </c>
     </row>
     <row r="93">
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>30.58529316266471</v>
+        <v>29.21456109072558</v>
       </c>
     </row>
     <row r="94">
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>22.53460041367748</v>
+        <v>26.06521223485701</v>
       </c>
     </row>
     <row r="95">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>26.72316359096767</v>
+        <v>29.29203351986684</v>
       </c>
     </row>
     <row r="96">
@@ -1967,7 +1967,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>30.85539838633474</v>
+        <v>27.73377927709425</v>
       </c>
     </row>
     <row r="97">
@@ -1983,7 +1983,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>30.05987245345765</v>
+        <v>24.65096473527565</v>
       </c>
     </row>
     <row r="98">
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>27.66950683805296</v>
+        <v>27.03923875226829</v>
       </c>
     </row>
     <row r="99">
@@ -2015,7 +2015,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>27.13782391973364</v>
+        <v>26.67794473620141</v>
       </c>
     </row>
     <row r="100">
@@ -2031,7 +2031,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>21.7228483936089</v>
+        <v>22.9481869133962</v>
       </c>
     </row>
     <row r="101">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>24.74560458124206</v>
+        <v>23.12666758924739</v>
       </c>
     </row>
     <row r="102">
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>32.1508755266154</v>
+        <v>30.76792366672925</v>
       </c>
     </row>
     <row r="103">
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>31.33743567651315</v>
+        <v>24.63426156629026</v>
       </c>
     </row>
     <row r="104">
@@ -2095,7 +2095,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>27.62646636716737</v>
+        <v>27.63501709890329</v>
       </c>
     </row>
     <row r="105">
@@ -2111,7 +2111,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>27.1660648574326</v>
+        <v>27.35402349373688</v>
       </c>
     </row>
     <row r="106">
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>21.76288084093663</v>
+        <v>22.74444997687952</v>
       </c>
     </row>
     <row r="107">
@@ -2143,7 +2143,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>24.78885832333376</v>
+        <v>23.11095315481912</v>
       </c>
     </row>
     <row r="108">
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>32.78889305319687</v>
+        <v>30.86802955632411</v>
       </c>
     </row>
     <row r="109">
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>31.61906377743652</v>
+        <v>24.59315529224313</v>
       </c>
     </row>
     <row r="110">
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>27.23001475995352</v>
+        <v>27.22301941317047</v>
       </c>
     </row>
     <row r="111">
@@ -2207,7 +2207,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>27.22243909200669</v>
+        <v>26.55678214169797</v>
       </c>
     </row>
     <row r="112">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>21.79698051122132</v>
+        <v>22.82317615488976</v>
       </c>
     </row>
     <row r="113">
@@ -2239,7 +2239,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>24.77727288241</v>
+        <v>22.99543345661297</v>
       </c>
     </row>
     <row r="114">
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>32.60464645942106</v>
+        <v>30.61774578472614</v>
       </c>
     </row>
     <row r="115">
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>32.49483021700793</v>
+        <v>24.40907321074276</v>
       </c>
     </row>
     <row r="116">
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>27.7680198336144</v>
+        <v>27.29606686462992</v>
       </c>
     </row>
     <row r="117">
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>27.79221006186055</v>
+        <v>27.07887865719928</v>
       </c>
     </row>
     <row r="118">
@@ -2319,7 +2319,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>21.8921716847523</v>
+        <v>23.00823818347956</v>
       </c>
     </row>
     <row r="119">
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>24.8111934441087</v>
+        <v>23.05835615920378</v>
       </c>
     </row>
     <row r="120">
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>32.33531176172219</v>
+        <v>30.24391746631318</v>
       </c>
     </row>
     <row r="121">
@@ -2367,7 +2367,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>31.52681254180862</v>
+        <v>24.33286668439056</v>
       </c>
     </row>
     <row r="122">
@@ -2383,7 +2383,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>27.39701461809451</v>
+        <v>27.04526070252859</v>
       </c>
     </row>
     <row r="123">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>27.41507674545921</v>
+        <v>27.09559652789568</v>
       </c>
     </row>
     <row r="124">
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>21.58004109099569</v>
+        <v>23.34450102894973</v>
       </c>
     </row>
     <row r="125">
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>24.67080393674179</v>
+        <v>23.15661924900693</v>
       </c>
     </row>
     <row r="126">
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>33.1883966328481</v>
+        <v>30.2404066376041</v>
       </c>
     </row>
     <row r="127">
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>30.70508122922451</v>
+        <v>24.34852043349424</v>
       </c>
     </row>
     <row r="128">
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>27.79987385755037</v>
+        <v>26.92446261754661</v>
       </c>
     </row>
     <row r="129">
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>27.03697804640046</v>
+        <v>27.12321865113174</v>
       </c>
     </row>
     <row r="130">
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>21.5829537906816</v>
+        <v>22.47698511745458</v>
       </c>
     </row>
     <row r="131">
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>24.91905454203809</v>
+        <v>23.18106424560805</v>
       </c>
     </row>
     <row r="132">
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>32.45842834817261</v>
+        <v>30.58006343868893</v>
       </c>
     </row>
     <row r="133">
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>30.95211692543657</v>
+        <v>24.48978326755017</v>
       </c>
     </row>
     <row r="134">
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>27.41289653274493</v>
+        <v>26.88829151295459</v>
       </c>
     </row>
     <row r="135">
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>27.66690937920993</v>
+        <v>26.92902833764393</v>
       </c>
     </row>
     <row r="136">
@@ -2607,7 +2607,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>21.52691145292214</v>
+        <v>22.50363448719939</v>
       </c>
     </row>
     <row r="137">
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>24.70397984009355</v>
+        <v>23.0521242130268</v>
       </c>
     </row>
     <row r="138">
@@ -2639,7 +2639,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>32.45235986805462</v>
+        <v>30.36653044943221</v>
       </c>
     </row>
     <row r="139">
@@ -2655,7 +2655,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>31.0854546885606</v>
+        <v>24.53470808270899</v>
       </c>
     </row>
     <row r="140">
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>28.20234613567843</v>
+        <v>26.73711891793998</v>
       </c>
     </row>
     <row r="141">
@@ -2687,7 +2687,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>27.65435679439516</v>
+        <v>27.20412191324203</v>
       </c>
     </row>
     <row r="142">
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>21.24613548561328</v>
+        <v>23.16990133410827</v>
       </c>
     </row>
     <row r="143">
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>24.69658359988992</v>
+        <v>22.68686752226902</v>
       </c>
     </row>
     <row r="144">
@@ -2735,7 +2735,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>32.22290997000602</v>
+        <v>30.66242492926081</v>
       </c>
     </row>
     <row r="145">
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>31.55605684267644</v>
+        <v>24.59844365687803</v>
       </c>
     </row>
     <row r="146">
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>28.5629946491987</v>
+        <v>24.11770337116348</v>
       </c>
     </row>
     <row r="147">
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>30.77454194026616</v>
+        <v>29.17940639776393</v>
       </c>
     </row>
     <row r="148">
@@ -2799,7 +2799,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>27.54879943231923</v>
+        <v>22.43168935963016</v>
       </c>
     </row>
     <row r="149">
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>26.42043769967777</v>
+        <v>28.06163253377404</v>
       </c>
     </row>
     <row r="150">
@@ -2831,7 +2831,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>30.71108443900398</v>
+        <v>32.08780884263879</v>
       </c>
     </row>
     <row r="151">
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>31.89130775774083</v>
+        <v>26.05884150418225</v>
       </c>
     </row>
     <row r="152">
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>28.65442833239878</v>
+        <v>24.55212360623565</v>
       </c>
     </row>
     <row r="153">
@@ -2879,7 +2879,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>30.60860208239184</v>
+        <v>29.61207311440213</v>
       </c>
     </row>
     <row r="154">
@@ -2895,7 +2895,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>27.89429822245935</v>
+        <v>22.27884226993119</v>
       </c>
     </row>
     <row r="155">
@@ -2911,7 +2911,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>26.29974423851887</v>
+        <v>27.73271542466532</v>
       </c>
     </row>
     <row r="156">
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>30.69225129262015</v>
+        <v>32.35498825397956</v>
       </c>
     </row>
     <row r="157">
@@ -2943,7 +2943,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>32.2920432197155</v>
+        <v>26.3504320742778</v>
       </c>
     </row>
     <row r="158">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>29.40216425950368</v>
+        <v>24.30688026860792</v>
       </c>
     </row>
     <row r="159">
@@ -2975,7 +2975,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>31.12799354698901</v>
+        <v>29.20224053196762</v>
       </c>
     </row>
     <row r="160">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>26.99391540885022</v>
+        <v>22.61686660705121</v>
       </c>
     </row>
     <row r="161">
@@ -3007,7 +3007,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>26.06682603775835</v>
+        <v>28.34098736099176</v>
       </c>
     </row>
     <row r="162">
@@ -3023,7 +3023,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>31.4779958449378</v>
+        <v>31.95372168697618</v>
       </c>
     </row>
     <row r="163">
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>31.77190010906777</v>
+        <v>26.13639994147664</v>
       </c>
     </row>
     <row r="164">
@@ -3055,7 +3055,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>28.918951456341</v>
+        <v>23.88820726177315</v>
       </c>
     </row>
     <row r="165">
@@ -3071,7 +3071,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>31.04855603023831</v>
+        <v>29.47460577850429</v>
       </c>
     </row>
     <row r="166">
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>27.15630532847723</v>
+        <v>22.19450032422421</v>
       </c>
     </row>
     <row r="167">
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>26.17807281493502</v>
+        <v>28.00280137929419</v>
       </c>
     </row>
     <row r="168">
@@ -3119,7 +3119,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>30.07666522131515</v>
+        <v>31.99533446687161</v>
       </c>
     </row>
     <row r="169">
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>31.67055554209665</v>
+        <v>26.48910142389136</v>
       </c>
     </row>
     <row r="170">
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>28.7184533199484</v>
+        <v>23.80244273412687</v>
       </c>
     </row>
     <row r="171">
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>30.42545146191644</v>
+        <v>29.35109449734938</v>
       </c>
     </row>
     <row r="172">
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>27.85783064738067</v>
+        <v>22.5792103518097</v>
       </c>
     </row>
     <row r="173">
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>25.81905825001109</v>
+        <v>28.17033389997033</v>
       </c>
     </row>
     <row r="174">
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>30.94740256620453</v>
+        <v>32.08720590981216</v>
       </c>
     </row>
     <row r="175">
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>32.04017742706655</v>
+        <v>26.52884735050497</v>
       </c>
     </row>
     <row r="176">
@@ -3247,7 +3247,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>29.2061300995677</v>
+        <v>24.36928301793637</v>
       </c>
     </row>
     <row r="177">
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>30.36750453441212</v>
+        <v>28.48353735524744</v>
       </c>
     </row>
     <row r="178">
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>27.72920810796261</v>
+        <v>22.90086433356257</v>
       </c>
     </row>
     <row r="179">
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>26.19634510079635</v>
+        <v>28.25524061803905</v>
       </c>
     </row>
     <row r="180">
@@ -3311,7 +3311,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>30.77909283381314</v>
+        <v>31.97727916361345</v>
       </c>
     </row>
     <row r="181">
@@ -3327,7 +3327,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>32.14620806212114</v>
+        <v>26.39941884853734</v>
       </c>
     </row>
     <row r="182">
@@ -3343,7 +3343,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>28.84848226405982</v>
+        <v>24.39226789538112</v>
       </c>
     </row>
     <row r="183">
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>30.62496594179443</v>
+        <v>29.26177674894465</v>
       </c>
     </row>
     <row r="184">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>27.42951351477685</v>
+        <v>22.00541344843383</v>
       </c>
     </row>
     <row r="185">
@@ -3391,7 +3391,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>26.09273693554986</v>
+        <v>28.72650785457624</v>
       </c>
     </row>
     <row r="186">
@@ -3407,7 +3407,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>31.1194727601923</v>
+        <v>32.15169166486512</v>
       </c>
     </row>
     <row r="187">
@@ -3423,7 +3423,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>32.21021345097125</v>
+        <v>26.77341006598747</v>
       </c>
     </row>
     <row r="188">
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>29.24780345545017</v>
+        <v>24.1044475149594</v>
       </c>
     </row>
     <row r="189">
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>30.42852249433754</v>
+        <v>29.74588411573905</v>
       </c>
     </row>
     <row r="190">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>27.99505306182169</v>
+        <v>22.5258535707546</v>
       </c>
     </row>
     <row r="191">
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>25.68234135450083</v>
+        <v>28.31680892763319</v>
       </c>
     </row>
     <row r="192">
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>31.03700565402474</v>
+        <v>31.85083314575826</v>
       </c>
     </row>
     <row r="193">
@@ -3519,7 +3519,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>32.18659436457719</v>
+        <v>26.82402359201912</v>
       </c>
     </row>
     <row r="194">
@@ -3535,7 +3535,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>28.97730019028065</v>
+        <v>32.52710265226822</v>
       </c>
     </row>
     <row r="195">
@@ -3551,7 +3551,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>32.17936589084081</v>
+        <v>24.86199315381285</v>
       </c>
     </row>
     <row r="196">
@@ -3567,7 +3567,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>15.7501461715677</v>
+        <v>27.3959741096832</v>
       </c>
     </row>
     <row r="197">
@@ -3583,7 +3583,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>30.1519411868662</v>
+        <v>25.95706769449076</v>
       </c>
     </row>
     <row r="198">
@@ -3599,7 +3599,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>30.0827927034048</v>
+        <v>28.01859623899067</v>
       </c>
     </row>
     <row r="199">
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>25.04486042480135</v>
+        <v>23.49081219585264</v>
       </c>
     </row>
     <row r="200">
@@ -3631,7 +3631,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>28.99926805443888</v>
+        <v>32.26034443770039</v>
       </c>
     </row>
     <row r="201">
@@ -3647,7 +3647,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>32.15663116474247</v>
+        <v>24.82150912587311</v>
       </c>
     </row>
     <row r="202">
@@ -3663,7 +3663,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>15.92497788925971</v>
+        <v>27.59607432633018</v>
       </c>
     </row>
     <row r="203">
@@ -3679,7 +3679,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>30.39444284497853</v>
+        <v>26.23458082394956</v>
       </c>
     </row>
     <row r="204">
@@ -3695,7 +3695,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>30.507122558296</v>
+        <v>27.27820901595326</v>
       </c>
     </row>
     <row r="205">
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>24.99023254966304</v>
+        <v>23.83034677592077</v>
       </c>
     </row>
     <row r="206">
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>28.65655722203655</v>
+        <v>31.88219812808433</v>
       </c>
     </row>
     <row r="207">
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>32.19961000112582</v>
+        <v>24.9494342211549</v>
       </c>
     </row>
     <row r="208">
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>15.90093939961181</v>
+        <v>27.53655559854105</v>
       </c>
     </row>
     <row r="209">
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>30.48627730236517</v>
+        <v>25.90512404938458</v>
       </c>
     </row>
     <row r="210">
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>30.25481614385098</v>
+        <v>27.57011494242103</v>
       </c>
     </row>
     <row r="211">
@@ -3807,7 +3807,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>24.86300826459261</v>
+        <v>23.63309997498248</v>
       </c>
     </row>
     <row r="212">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>29.26529986985653</v>
+        <v>31.87323963301423</v>
       </c>
     </row>
     <row r="213">
@@ -3839,7 +3839,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>32.1894454916311</v>
+        <v>24.21196972475513</v>
       </c>
     </row>
     <row r="214">
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>15.86934244140877</v>
+        <v>27.76039963961734</v>
       </c>
     </row>
     <row r="215">
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>30.24005995544189</v>
+        <v>26.04091095270545</v>
       </c>
     </row>
     <row r="216">
@@ -3887,7 +3887,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>30.1952683884298</v>
+        <v>27.35099089266383</v>
       </c>
     </row>
     <row r="217">
@@ -3903,7 +3903,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>25.10674016284441</v>
+        <v>23.99836948298175</v>
       </c>
     </row>
     <row r="218">
@@ -3919,7 +3919,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>29.13461765723405</v>
+        <v>31.94024922379822</v>
       </c>
     </row>
     <row r="219">
@@ -3935,7 +3935,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>32.64442480970493</v>
+        <v>24.36316120536429</v>
       </c>
     </row>
     <row r="220">
@@ -3951,7 +3951,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>15.98903773708224</v>
+        <v>27.4630243764161</v>
       </c>
     </row>
     <row r="221">
@@ -3967,7 +3967,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>30.30769145498891</v>
+        <v>26.10714102860301</v>
       </c>
     </row>
     <row r="222">
@@ -3983,7 +3983,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>30.46750795630783</v>
+        <v>27.376058800454</v>
       </c>
     </row>
     <row r="223">
@@ -3999,7 +3999,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>24.75682008606106</v>
+        <v>23.67437215504787</v>
       </c>
     </row>
     <row r="224">
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>28.98977593450654</v>
+        <v>32.28435403079055</v>
       </c>
     </row>
     <row r="225">
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>32.33886061093406</v>
+        <v>24.51615231877133</v>
       </c>
     </row>
     <row r="226">
@@ -4047,7 +4047,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>15.79830296147626</v>
+        <v>27.37074371395212</v>
       </c>
     </row>
     <row r="227">
@@ -4063,7 +4063,7 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>30.48166748876465</v>
+        <v>25.8704825910399</v>
       </c>
     </row>
     <row r="228">
@@ -4079,7 +4079,7 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>30.01353828839505</v>
+        <v>27.46279201792024</v>
       </c>
     </row>
     <row r="229">
@@ -4095,7 +4095,7 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>25.35349209701874</v>
+        <v>23.53096091582784</v>
       </c>
     </row>
     <row r="230">
@@ -4111,7 +4111,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>28.60540465286982</v>
+        <v>31.93038691014735</v>
       </c>
     </row>
     <row r="231">
@@ -4127,7 +4127,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>31.98783579441977</v>
+        <v>24.4658434156798</v>
       </c>
     </row>
     <row r="232">
@@ -4143,7 +4143,7 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>15.96577866481706</v>
+        <v>27.52566497215417</v>
       </c>
     </row>
     <row r="233">
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>30.54121131398233</v>
+        <v>26.67114236795509</v>
       </c>
     </row>
     <row r="234">
@@ -4175,7 +4175,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>30.45000698383927</v>
+        <v>27.19460799943478</v>
       </c>
     </row>
     <row r="235">
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>24.98991384848164</v>
+        <v>23.96643985588792</v>
       </c>
     </row>
     <row r="236">
@@ -4207,7 +4207,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>28.89256564630306</v>
+        <v>32.54563566217971</v>
       </c>
     </row>
     <row r="237">
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>32.09046227818327</v>
+        <v>24.25069103358334</v>
       </c>
     </row>
     <row r="238">
@@ -4239,7 +4239,7 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>15.79495832299273</v>
+        <v>27.78231153772408</v>
       </c>
     </row>
     <row r="239">
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>30.09613802764359</v>
+        <v>25.77374570156145</v>
       </c>
     </row>
     <row r="240">
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>30.55622356415909</v>
+        <v>26.65932486917626</v>
       </c>
     </row>
     <row r="241">
@@ -4287,7 +4287,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>24.79735129227493</v>
+        <v>23.88644163746902</v>
       </c>
     </row>
     <row r="242">
@@ -4303,7 +4303,7 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>29.02451536523277</v>
+        <v>27.60315390019853</v>
       </c>
     </row>
     <row r="243">
@@ -4319,7 +4319,7 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>22.36270474569161</v>
+        <v>28.28423376042332</v>
       </c>
     </row>
     <row r="244">
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>25.24710414769315</v>
+        <v>21.30915481988835</v>
       </c>
     </row>
     <row r="245">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>28.83643555795685</v>
+        <v>31.02884747118719</v>
       </c>
     </row>
     <row r="246">
@@ -4367,7 +4367,7 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>34.15056137677244</v>
+        <v>31.732467079799</v>
       </c>
     </row>
     <row r="247">
@@ -4383,7 +4383,7 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>24.03717928657334</v>
+        <v>19.91793324658343</v>
       </c>
     </row>
     <row r="248">
@@ -4399,7 +4399,7 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>29.3377984289354</v>
+        <v>27.90323937856514</v>
       </c>
     </row>
     <row r="249">
@@ -4415,7 +4415,7 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>22.32107531592501</v>
+        <v>27.81541199133747</v>
       </c>
     </row>
     <row r="250">
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>25.02484515905266</v>
+        <v>21.36131163300656</v>
       </c>
     </row>
     <row r="251">
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>29.0672094852888</v>
+        <v>30.43674317845695</v>
       </c>
     </row>
     <row r="252">
@@ -4463,7 +4463,7 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>33.93505337503788</v>
+        <v>31.28248453330482</v>
       </c>
     </row>
     <row r="253">
@@ -4479,7 +4479,7 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>23.64125398313965</v>
+        <v>20.04000394886682</v>
       </c>
     </row>
     <row r="254">
@@ -4495,7 +4495,7 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>29.0558456028002</v>
+        <v>28.25904193588427</v>
       </c>
     </row>
     <row r="255">
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>22.38692058250046</v>
+        <v>28.25571608314407</v>
       </c>
     </row>
     <row r="256">
@@ -4527,7 +4527,7 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>25.22145199606594</v>
+        <v>21.29196154540897</v>
       </c>
     </row>
     <row r="257">
@@ -4543,7 +4543,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>29.42776725204962</v>
+        <v>30.0834669328224</v>
       </c>
     </row>
     <row r="258">
@@ -4559,7 +4559,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>34.72900592267152</v>
+        <v>31.82540921050645</v>
       </c>
     </row>
     <row r="259">
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>23.94039489463883</v>
+        <v>19.87070015185002</v>
       </c>
     </row>
     <row r="260">
@@ -4591,7 +4591,7 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>29.26054094834307</v>
+        <v>27.91322600080922</v>
       </c>
     </row>
     <row r="261">
@@ -4607,7 +4607,7 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>22.20989151065052</v>
+        <v>28.0105103130684</v>
       </c>
     </row>
     <row r="262">
@@ -4623,7 +4623,7 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>25.13862482788148</v>
+        <v>21.06046817342797</v>
       </c>
     </row>
     <row r="263">
@@ -4639,7 +4639,7 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>28.91620443972791</v>
+        <v>30.37642543633876</v>
       </c>
     </row>
     <row r="264">
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>34.54480601747952</v>
+        <v>31.24638984409154</v>
       </c>
     </row>
     <row r="265">
@@ -4671,7 +4671,7 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>23.78038654071459</v>
+        <v>20.1327749418448</v>
       </c>
     </row>
     <row r="266">
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>29.41809875462659</v>
+        <v>28.29273965336353</v>
       </c>
     </row>
     <row r="267">
@@ -4703,7 +4703,7 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>22.7786740566631</v>
+        <v>28.15832473739917</v>
       </c>
     </row>
     <row r="268">
@@ -4719,7 +4719,7 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>25.11593376917311</v>
+        <v>21.65585222181002</v>
       </c>
     </row>
     <row r="269">
@@ -4735,7 +4735,7 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>29.11641125899098</v>
+        <v>30.62607934387334</v>
       </c>
     </row>
     <row r="270">
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>34.6713241225988</v>
+        <v>31.39206360860015</v>
       </c>
     </row>
     <row r="271">
@@ -4767,7 +4767,7 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>23.88253851028252</v>
+        <v>20.04084917685917</v>
       </c>
     </row>
     <row r="272">
@@ -4783,7 +4783,7 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>29.33168939578223</v>
+        <v>28.04293070247386</v>
       </c>
     </row>
     <row r="273">
@@ -4799,7 +4799,7 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>22.43763211993449</v>
+        <v>28.04608414228754</v>
       </c>
     </row>
     <row r="274">
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>25.16783861203077</v>
+        <v>21.39847093917997</v>
       </c>
     </row>
     <row r="275">
@@ -4831,7 +4831,7 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>28.7757430184253</v>
+        <v>30.17801900108089</v>
       </c>
     </row>
     <row r="276">
@@ -4847,7 +4847,7 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>34.44212188971942</v>
+        <v>31.48503756584726</v>
       </c>
     </row>
     <row r="277">
@@ -4863,7 +4863,7 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>24.09815989481555</v>
+        <v>19.80993899987949</v>
       </c>
     </row>
     <row r="278">
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="D278" t="n">
-        <v>29.69079948207868</v>
+        <v>28.33296656522022</v>
       </c>
     </row>
     <row r="279">
@@ -4895,7 +4895,7 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>22.65001759793227</v>
+        <v>28.08702224985547</v>
       </c>
     </row>
     <row r="280">
@@ -4911,7 +4911,7 @@
         </is>
       </c>
       <c r="D280" t="n">
-        <v>25.68466032383</v>
+        <v>21.46653522244436</v>
       </c>
     </row>
     <row r="281">
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>28.7773850577043</v>
+        <v>30.67304457578296</v>
       </c>
     </row>
     <row r="282">
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>34.73405424946419</v>
+        <v>31.59896868020972</v>
       </c>
     </row>
     <row r="283">
@@ -4959,7 +4959,7 @@
         </is>
       </c>
       <c r="D283" t="n">
-        <v>24.02270926287277</v>
+        <v>19.69438908878039</v>
       </c>
     </row>
     <row r="284">
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="D284" t="n">
-        <v>29.90697630509682</v>
+        <v>28.03836497030531</v>
       </c>
     </row>
     <row r="285">
@@ -4991,7 +4991,7 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>22.25346687849758</v>
+        <v>28.40509724902088</v>
       </c>
     </row>
     <row r="286">
@@ -5007,7 +5007,7 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>24.93214602647758</v>
+        <v>21.09157146917317</v>
       </c>
     </row>
     <row r="287">
@@ -5023,7 +5023,7 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>28.82609184133769</v>
+        <v>30.64052112686559</v>
       </c>
     </row>
     <row r="288">
@@ -5039,7 +5039,7 @@
         </is>
       </c>
       <c r="D288" t="n">
-        <v>33.70234663165332</v>
+        <v>30.68880810410976</v>
       </c>
     </row>
     <row r="289">
@@ -5055,7 +5055,7 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>23.85267668671973</v>
+        <v>19.80405981179928</v>
       </c>
     </row>
     <row r="290">
@@ -5071,7 +5071,7 @@
         </is>
       </c>
       <c r="D290" t="n">
-        <v>26.45301894287697</v>
+        <v>33.32880149014309</v>
       </c>
     </row>
     <row r="291">
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="D291" t="n">
-        <v>26.63507762620971</v>
+        <v>32.75666291378825</v>
       </c>
     </row>
     <row r="292">
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="D292" t="n">
-        <v>29.67112573435474</v>
+        <v>30.29570123865987</v>
       </c>
     </row>
     <row r="293">
@@ -5119,7 +5119,7 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>29.46310115289606</v>
+        <v>27.09151160845332</v>
       </c>
     </row>
     <row r="294">
@@ -5135,7 +5135,7 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>28.68074163836922</v>
+        <v>27.22924027115272</v>
       </c>
     </row>
     <row r="295">
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>27.84019991018853</v>
+        <v>30.1618145908331</v>
       </c>
     </row>
     <row r="296">
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="D296" t="n">
-        <v>26.41589280984012</v>
+        <v>33.50492940159998</v>
       </c>
     </row>
     <row r="297">
@@ -5183,7 +5183,7 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>26.72590657652815</v>
+        <v>33.23431997998192</v>
       </c>
     </row>
     <row r="298">
@@ -5199,7 +5199,7 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>29.1796743985436</v>
+        <v>30.48909996596163</v>
       </c>
     </row>
     <row r="299">
@@ -5215,7 +5215,7 @@
         </is>
       </c>
       <c r="D299" t="n">
-        <v>29.45017019633031</v>
+        <v>27.05174131478679</v>
       </c>
     </row>
     <row r="300">
@@ -5231,7 +5231,7 @@
         </is>
       </c>
       <c r="D300" t="n">
-        <v>28.74580681175474</v>
+        <v>26.70956549528053</v>
       </c>
     </row>
     <row r="301">
@@ -5247,7 +5247,7 @@
         </is>
       </c>
       <c r="D301" t="n">
-        <v>27.8703656288721</v>
+        <v>29.88305844562662</v>
       </c>
     </row>
     <row r="302">
@@ -5263,7 +5263,7 @@
         </is>
       </c>
       <c r="D302" t="n">
-        <v>26.1987262290957</v>
+        <v>33.60175670776272</v>
       </c>
     </row>
     <row r="303">
@@ -5279,7 +5279,7 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>26.95514372273376</v>
+        <v>33.68857349052659</v>
       </c>
     </row>
     <row r="304">
@@ -5295,7 +5295,7 @@
         </is>
       </c>
       <c r="D304" t="n">
-        <v>29.5361987486131</v>
+        <v>31.04597294171916</v>
       </c>
     </row>
     <row r="305">
@@ -5311,7 +5311,7 @@
         </is>
       </c>
       <c r="D305" t="n">
-        <v>29.27848581201093</v>
+        <v>27.73062993527815</v>
       </c>
     </row>
     <row r="306">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="D306" t="n">
-        <v>27.95773102070302</v>
+        <v>26.62737626256162</v>
       </c>
     </row>
     <row r="307">
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="D307" t="n">
-        <v>27.83390753567346</v>
+        <v>29.77633879802872</v>
       </c>
     </row>
     <row r="308">
@@ -5359,7 +5359,7 @@
         </is>
       </c>
       <c r="D308" t="n">
-        <v>26.65676627909538</v>
+        <v>33.5713523413819</v>
       </c>
     </row>
     <row r="309">
@@ -5375,7 +5375,7 @@
         </is>
       </c>
       <c r="D309" t="n">
-        <v>26.60757480459009</v>
+        <v>33.42716544926988</v>
       </c>
     </row>
     <row r="310">
@@ -5391,7 +5391,7 @@
         </is>
       </c>
       <c r="D310" t="n">
-        <v>29.43698359191132</v>
+        <v>30.05611636748434</v>
       </c>
     </row>
     <row r="311">
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="D311" t="n">
-        <v>29.10063444108391</v>
+        <v>27.59395448160425</v>
       </c>
     </row>
     <row r="312">
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="D312" t="n">
-        <v>28.10740074437057</v>
+        <v>27.0059336051587</v>
       </c>
     </row>
     <row r="313">
@@ -5439,7 +5439,7 @@
         </is>
       </c>
       <c r="D313" t="n">
-        <v>27.96187425167716</v>
+        <v>30.1301056216003</v>
       </c>
     </row>
     <row r="314">
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c r="D314" t="n">
-        <v>26.68743379559405</v>
+        <v>33.2542790079909</v>
       </c>
     </row>
     <row r="315">
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="D315" t="n">
-        <v>26.73189569886224</v>
+        <v>33.03947417963319</v>
       </c>
     </row>
     <row r="316">
@@ -5487,7 +5487,7 @@
         </is>
       </c>
       <c r="D316" t="n">
-        <v>29.78049326423044</v>
+        <v>30.15464062907622</v>
       </c>
     </row>
     <row r="317">
@@ -5503,7 +5503,7 @@
         </is>
       </c>
       <c r="D317" t="n">
-        <v>28.59525095593398</v>
+        <v>27.71626206818082</v>
       </c>
     </row>
     <row r="318">
@@ -5519,7 +5519,7 @@
         </is>
       </c>
       <c r="D318" t="n">
-        <v>27.97486651654892</v>
+        <v>26.70493735509944</v>
       </c>
     </row>
     <row r="319">
@@ -5535,7 +5535,7 @@
         </is>
       </c>
       <c r="D319" t="n">
-        <v>28.35951476904194</v>
+        <v>30.04205940937669</v>
       </c>
     </row>
     <row r="320">
@@ -5551,7 +5551,7 @@
         </is>
       </c>
       <c r="D320" t="n">
-        <v>26.74394807625156</v>
+        <v>33.89320356333618</v>
       </c>
     </row>
     <row r="321">
@@ -5567,7 +5567,7 @@
         </is>
       </c>
       <c r="D321" t="n">
-        <v>26.39601968269633</v>
+        <v>33.53648667351151</v>
       </c>
     </row>
     <row r="322">
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="D322" t="n">
-        <v>30.02874495700152</v>
+        <v>30.71070254435915</v>
       </c>
     </row>
     <row r="323">
@@ -5599,7 +5599,7 @@
         </is>
       </c>
       <c r="D323" t="n">
-        <v>28.95395679325184</v>
+        <v>27.53527207266259</v>
       </c>
     </row>
     <row r="324">
@@ -5615,7 +5615,7 @@
         </is>
       </c>
       <c r="D324" t="n">
-        <v>28.74576620242208</v>
+        <v>27.19491443924268</v>
       </c>
     </row>
     <row r="325">
@@ -5631,7 +5631,7 @@
         </is>
       </c>
       <c r="D325" t="n">
-        <v>28.02064934077672</v>
+        <v>30.63017068763752</v>
       </c>
     </row>
     <row r="326">
@@ -5647,7 +5647,7 @@
         </is>
       </c>
       <c r="D326" t="n">
-        <v>27.2046685059067</v>
+        <v>33.62560464695411</v>
       </c>
     </row>
     <row r="327">
@@ -5663,7 +5663,7 @@
         </is>
       </c>
       <c r="D327" t="n">
-        <v>27.06191458416295</v>
+        <v>33.50241991090085</v>
       </c>
     </row>
     <row r="328">
@@ -5679,7 +5679,7 @@
         </is>
       </c>
       <c r="D328" t="n">
-        <v>29.4964493903923</v>
+        <v>29.95634959191802</v>
       </c>
     </row>
     <row r="329">
@@ -5695,7 +5695,7 @@
         </is>
       </c>
       <c r="D329" t="n">
-        <v>29.20148631410503</v>
+        <v>27.53022929764786</v>
       </c>
     </row>
     <row r="330">
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="D330" t="n">
-        <v>28.59407533873767</v>
+        <v>26.75288942007865</v>
       </c>
     </row>
     <row r="331">
@@ -5727,7 +5727,7 @@
         </is>
       </c>
       <c r="D331" t="n">
-        <v>28.38498368035059</v>
+        <v>30.14065327132576</v>
       </c>
     </row>
     <row r="332">
@@ -5743,7 +5743,7 @@
         </is>
       </c>
       <c r="D332" t="n">
-        <v>26.39816464695118</v>
+        <v>33.6301159491717</v>
       </c>
     </row>
     <row r="333">
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="D333" t="n">
-        <v>26.77753621449802</v>
+        <v>32.39594460603396</v>
       </c>
     </row>
     <row r="334">
@@ -5775,7 +5775,7 @@
         </is>
       </c>
       <c r="D334" t="n">
-        <v>29.88304510226989</v>
+        <v>30.42304655030881</v>
       </c>
     </row>
     <row r="335">
@@ -5791,7 +5791,7 @@
         </is>
       </c>
       <c r="D335" t="n">
-        <v>28.41186679923126</v>
+        <v>27.57042392919989</v>
       </c>
     </row>
     <row r="336">
@@ -5807,7 +5807,7 @@
         </is>
       </c>
       <c r="D336" t="n">
-        <v>28.07454713302252</v>
+        <v>26.66268475442084</v>
       </c>
     </row>
     <row r="337">
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="D337" t="n">
-        <v>27.43072243577382</v>
+        <v>29.68569784080108</v>
       </c>
     </row>
     <row r="338">
@@ -5839,7 +5839,7 @@
         </is>
       </c>
       <c r="D338" t="n">
-        <v>29.2026384638177</v>
+        <v>28.07262622965318</v>
       </c>
     </row>
     <row r="339">
@@ -5855,7 +5855,7 @@
         </is>
       </c>
       <c r="D339" t="n">
-        <v>30.93257902903899</v>
+        <v>31.50984723020773</v>
       </c>
     </row>
     <row r="340">
@@ -5871,7 +5871,7 @@
         </is>
       </c>
       <c r="D340" t="n">
-        <v>23.61147112517853</v>
+        <v>26.55189721164252</v>
       </c>
     </row>
     <row r="341">
@@ -5887,7 +5887,7 @@
         </is>
       </c>
       <c r="D341" t="n">
-        <v>27.10261274250927</v>
+        <v>30.83134707701486</v>
       </c>
     </row>
     <row r="342">
@@ -5903,7 +5903,7 @@
         </is>
       </c>
       <c r="D342" t="n">
-        <v>29.29310240126282</v>
+        <v>31.32435847134334</v>
       </c>
     </row>
     <row r="343">
@@ -5919,7 +5919,7 @@
         </is>
       </c>
       <c r="D343" t="n">
-        <v>20.01223748859628</v>
+        <v>28.75715729001912</v>
       </c>
     </row>
     <row r="344">
@@ -5935,7 +5935,7 @@
         </is>
       </c>
       <c r="D344" t="n">
-        <v>28.78274854010469</v>
+        <v>28.05359033784703</v>
       </c>
     </row>
     <row r="345">
@@ -5951,7 +5951,7 @@
         </is>
       </c>
       <c r="D345" t="n">
-        <v>30.69514604979343</v>
+        <v>31.4474377715454</v>
       </c>
     </row>
     <row r="346">
@@ -5967,7 +5967,7 @@
         </is>
       </c>
       <c r="D346" t="n">
-        <v>23.35133421147205</v>
+        <v>26.70630254300941</v>
       </c>
     </row>
     <row r="347">
@@ -5983,7 +5983,7 @@
         </is>
       </c>
       <c r="D347" t="n">
-        <v>27.0736914193375</v>
+        <v>30.37824616815397</v>
       </c>
     </row>
     <row r="348">
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="D348" t="n">
-        <v>28.22776273769819</v>
+        <v>31.04240127629676</v>
       </c>
     </row>
     <row r="349">
@@ -6015,7 +6015,7 @@
         </is>
       </c>
       <c r="D349" t="n">
-        <v>20.27420720390161</v>
+        <v>28.8115055247354</v>
       </c>
     </row>
     <row r="350">
@@ -6031,7 +6031,7 @@
         </is>
       </c>
       <c r="D350" t="n">
-        <v>28.89955633159597</v>
+        <v>28.07453800285071</v>
       </c>
     </row>
     <row r="351">
@@ -6047,7 +6047,7 @@
         </is>
       </c>
       <c r="D351" t="n">
-        <v>30.9178771860367</v>
+        <v>31.38667615428671</v>
       </c>
     </row>
     <row r="352">
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="D352" t="n">
-        <v>23.34727099198109</v>
+        <v>26.93491593290616</v>
       </c>
     </row>
     <row r="353">
@@ -6079,7 +6079,7 @@
         </is>
       </c>
       <c r="D353" t="n">
-        <v>26.82800261414788</v>
+        <v>30.4381197613741</v>
       </c>
     </row>
     <row r="354">
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="D354" t="n">
-        <v>28.67556020763989</v>
+        <v>30.82594336279737</v>
       </c>
     </row>
     <row r="355">
@@ -6111,7 +6111,7 @@
         </is>
       </c>
       <c r="D355" t="n">
-        <v>20.07735300467299</v>
+        <v>28.72389221164843</v>
       </c>
     </row>
     <row r="356">
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="D356" t="n">
-        <v>29.2631714976385</v>
+        <v>27.53727545386684</v>
       </c>
     </row>
     <row r="357">
@@ -6143,7 +6143,7 @@
         </is>
       </c>
       <c r="D357" t="n">
-        <v>31.00555125030442</v>
+        <v>31.68059141342813</v>
       </c>
     </row>
     <row r="358">
@@ -6159,7 +6159,7 @@
         </is>
       </c>
       <c r="D358" t="n">
-        <v>23.03269341063235</v>
+        <v>26.93644818003083</v>
       </c>
     </row>
     <row r="359">
@@ -6175,7 +6175,7 @@
         </is>
       </c>
       <c r="D359" t="n">
-        <v>27.21905461889997</v>
+        <v>30.82036823910012</v>
       </c>
     </row>
     <row r="360">
@@ -6191,7 +6191,7 @@
         </is>
       </c>
       <c r="D360" t="n">
-        <v>28.67083580515452</v>
+        <v>31.17439365035071</v>
       </c>
     </row>
     <row r="361">
@@ -6207,7 +6207,7 @@
         </is>
       </c>
       <c r="D361" t="n">
-        <v>20.13139963433389</v>
+        <v>29.33679927287404</v>
       </c>
     </row>
     <row r="362">
@@ -6223,7 +6223,7 @@
         </is>
       </c>
       <c r="D362" t="n">
-        <v>29.25018477161604</v>
+        <v>27.70029826099104</v>
       </c>
     </row>
     <row r="363">
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="D363" t="n">
-        <v>30.39426021910589</v>
+        <v>30.73109068780914</v>
       </c>
     </row>
     <row r="364">
@@ -6255,7 +6255,7 @@
         </is>
       </c>
       <c r="D364" t="n">
-        <v>23.13320307159</v>
+        <v>26.86570932621427</v>
       </c>
     </row>
     <row r="365">
@@ -6271,7 +6271,7 @@
         </is>
       </c>
       <c r="D365" t="n">
-        <v>26.75813015836751</v>
+        <v>30.71903651166748</v>
       </c>
     </row>
     <row r="366">
@@ -6287,7 +6287,7 @@
         </is>
       </c>
       <c r="D366" t="n">
-        <v>29.38998153818003</v>
+        <v>30.90831068687062</v>
       </c>
     </row>
     <row r="367">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="D367" t="n">
-        <v>20.29944748511542</v>
+        <v>28.47416661083624</v>
       </c>
     </row>
     <row r="368">
@@ -6319,7 +6319,7 @@
         </is>
       </c>
       <c r="D368" t="n">
-        <v>29.07663459430304</v>
+        <v>27.7085569540809</v>
       </c>
     </row>
     <row r="369">
@@ -6335,7 +6335,7 @@
         </is>
       </c>
       <c r="D369" t="n">
-        <v>30.77792392441868</v>
+        <v>31.47982789278009</v>
       </c>
     </row>
     <row r="370">
@@ -6351,7 +6351,7 @@
         </is>
       </c>
       <c r="D370" t="n">
-        <v>23.23586319089648</v>
+        <v>26.67745583097788</v>
       </c>
     </row>
     <row r="371">
@@ -6367,7 +6367,7 @@
         </is>
       </c>
       <c r="D371" t="n">
-        <v>27.02270179610979</v>
+        <v>31.47604703266688</v>
       </c>
     </row>
     <row r="372">
@@ -6383,7 +6383,7 @@
         </is>
       </c>
       <c r="D372" t="n">
-        <v>29.00070095750247</v>
+        <v>30.77067913245468</v>
       </c>
     </row>
     <row r="373">
@@ -6399,7 +6399,7 @@
         </is>
       </c>
       <c r="D373" t="n">
-        <v>20.44600737647483</v>
+        <v>28.52756941918366</v>
       </c>
     </row>
     <row r="374">
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="D374" t="n">
-        <v>29.12618606751351</v>
+        <v>27.19384588854849</v>
       </c>
     </row>
     <row r="375">
@@ -6431,7 +6431,7 @@
         </is>
       </c>
       <c r="D375" t="n">
-        <v>30.53535948939236</v>
+        <v>31.50186975801262</v>
       </c>
     </row>
     <row r="376">
@@ -6447,7 +6447,7 @@
         </is>
       </c>
       <c r="D376" t="n">
-        <v>23.1980104275224</v>
+        <v>26.27162797647006</v>
       </c>
     </row>
     <row r="377">
@@ -6463,7 +6463,7 @@
         </is>
       </c>
       <c r="D377" t="n">
-        <v>26.4591271314441</v>
+        <v>30.5687901361153</v>
       </c>
     </row>
     <row r="378">
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="D378" t="n">
-        <v>28.38694178501519</v>
+        <v>30.98345083969878</v>
       </c>
     </row>
     <row r="379">
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="D379" t="n">
-        <v>20.56966181583805</v>
+        <v>28.55154857007047</v>
       </c>
     </row>
     <row r="380">
@@ -6511,7 +6511,7 @@
         </is>
       </c>
       <c r="D380" t="n">
-        <v>29.76319652362181</v>
+        <v>28.31472880229873</v>
       </c>
     </row>
     <row r="381">
@@ -6527,7 +6527,7 @@
         </is>
       </c>
       <c r="D381" t="n">
-        <v>30.63572151207531</v>
+        <v>31.73531321724617</v>
       </c>
     </row>
     <row r="382">
@@ -6543,7 +6543,7 @@
         </is>
       </c>
       <c r="D382" t="n">
-        <v>23.39611157388414</v>
+        <v>27.16596298729386</v>
       </c>
     </row>
     <row r="383">
@@ -6559,7 +6559,7 @@
         </is>
       </c>
       <c r="D383" t="n">
-        <v>27.16684045577297</v>
+        <v>30.46338150234816</v>
       </c>
     </row>
     <row r="384">
@@ -6575,7 +6575,7 @@
         </is>
       </c>
       <c r="D384" t="n">
-        <v>29.71112215511457</v>
+        <v>31.41974320089688</v>
       </c>
     </row>
     <row r="385">
@@ -6591,7 +6591,7 @@
         </is>
       </c>
       <c r="D385" t="n">
-        <v>20.51947910913864</v>
+        <v>28.89826357944132</v>
       </c>
     </row>
   </sheetData>
